--- a/app/src/main/assets/quantities_template.xlsx
+++ b/app/src/main/assets/quantities_template.xlsx
@@ -13,6 +13,7 @@
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
+    <sheet name="التقييم" sheetId="13" r:id="rIdEval99"/>
     <sheet name="الكميات  " sheetId="12" r:id="rId1"/>
     <sheet name="المخطط" sheetId="8" r:id="rId2"/>
     <sheet name="الوثائق" sheetId="3" r:id="rId3"/>
@@ -648,8 +649,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -816,8 +817,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -902,8 +928,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE9EF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="58">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -1659,6 +1701,27 @@
         <color indexed="64"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="4">
@@ -1667,7 +1730,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2095,12 +2158,55 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="20% - Accent1 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent1 2" xfId="3" ns2:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2" xfId="2" ns2:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 3" xfId="1" ns2:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2111,11 +2217,11 @@
     </mruColors>
   </colors>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4147,6 +4253,462 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="146" t="inlineStr">
+        <is>
+          <t>نموذج تقييم لمنزل السيد/ة</t>
+        </is>
+      </c>
+      <c r="D1" s="147" t="inlineStr"/>
+      <c r="E1" s="148" t="inlineStr">
+        <is>
+          <t>المهندس/ة - الباحث/ة الاجتماعي/ة</t>
+        </is>
+      </c>
+      <c r="G1" s="149" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="150" t="inlineStr">
+        <is>
+          <t>1. معلومات عامة</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="151" t="inlineStr">
+        <is>
+          <t>البلد:</t>
+        </is>
+      </c>
+      <c r="B3" s="152" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C3" s="151" t="inlineStr">
+        <is>
+          <t>عمر رب/ة الاسرة بالسنوات:</t>
+        </is>
+      </c>
+      <c r="D3" s="153" t="inlineStr"/>
+      <c r="E3" s="151" t="inlineStr">
+        <is>
+          <t>جنس رب/ة الاسرة:</t>
+        </is>
+      </c>
+      <c r="F3" s="153" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="151" t="inlineStr">
+        <is>
+          <t>المخيم:</t>
+        </is>
+      </c>
+      <c r="B4" s="152" t="inlineStr">
+        <is>
+          <t>Yarmouk</t>
+        </is>
+      </c>
+      <c r="C4" s="151" t="inlineStr">
+        <is>
+          <t>الحالة العائلية لرب/ة الاسرة:</t>
+        </is>
+      </c>
+      <c r="D4" s="153" t="inlineStr"/>
+      <c r="E4" s="151" t="inlineStr">
+        <is>
+          <t>السكن الحالي:</t>
+        </is>
+      </c>
+      <c r="F4" s="153" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="151" t="inlineStr">
+        <is>
+          <t>اسم رب/ة الاسرة:</t>
+        </is>
+      </c>
+      <c r="B5" s="153" t="inlineStr"/>
+      <c r="C5" s="151" t="inlineStr">
+        <is>
+          <t>اذا رب الاسرة متزوج من إمراة ثانية:</t>
+        </is>
+      </c>
+      <c r="D5" s="153" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="151" t="inlineStr">
+        <is>
+          <t>رقم العائلة:</t>
+        </is>
+      </c>
+      <c r="B6" s="153" t="inlineStr"/>
+      <c r="C6" s="151" t="inlineStr">
+        <is>
+          <t>وضع ملكية البيت:</t>
+        </is>
+      </c>
+      <c r="D6" s="153" t="inlineStr"/>
+      <c r="E6" s="151" t="inlineStr">
+        <is>
+          <t>اوراق الملكية المتوفرة:</t>
+        </is>
+      </c>
+      <c r="F6" s="153" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="151" t="inlineStr">
+        <is>
+          <t>رقم التسجيل في الكرت الابيض لرب العائلة:</t>
+        </is>
+      </c>
+      <c r="B7" s="153" t="inlineStr"/>
+      <c r="C7" s="151" t="inlineStr">
+        <is>
+          <t>رقم تعريف قطعة الأرض:</t>
+        </is>
+      </c>
+      <c r="D7" s="153" t="inlineStr"/>
+      <c r="E7" s="151" t="inlineStr">
+        <is>
+          <t>العنوان:</t>
+        </is>
+      </c>
+      <c r="F7" s="152" t="inlineStr">
+        <is>
+          <t>مخيم اليرموك</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="151" t="inlineStr">
+        <is>
+          <t>رقم السجل/ رقم الليدجر:</t>
+        </is>
+      </c>
+      <c r="B8" s="153" t="inlineStr"/>
+      <c r="C8" s="151" t="inlineStr">
+        <is>
+          <t>رقم المسكن:</t>
+        </is>
+      </c>
+      <c r="D8" s="153" t="inlineStr"/>
+      <c r="E8" s="151" t="inlineStr">
+        <is>
+          <t>اسم الشارع:</t>
+        </is>
+      </c>
+      <c r="F8" s="153" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="151" t="inlineStr">
+        <is>
+          <t>عدد افراد الاسرة المسجلين:</t>
+        </is>
+      </c>
+      <c r="B9" s="153" t="inlineStr"/>
+      <c r="C9" s="151" t="inlineStr">
+        <is>
+          <t>رقم الجوال 1:</t>
+        </is>
+      </c>
+      <c r="D9" s="153" t="inlineStr"/>
+      <c r="E9" s="151" t="inlineStr">
+        <is>
+          <t>عنوان المنزل:</t>
+        </is>
+      </c>
+      <c r="F9" s="153" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="151" t="inlineStr">
+        <is>
+          <t>رقم الهوية الوطني ل رب/ة الاسرة:</t>
+        </is>
+      </c>
+      <c r="B10" s="153" t="inlineStr"/>
+      <c r="C10" s="151" t="inlineStr">
+        <is>
+          <t>رقم الجوال 2:</t>
+        </is>
+      </c>
+      <c r="D10" s="153" t="inlineStr"/>
+      <c r="E10" s="151" t="inlineStr">
+        <is>
+          <t>الطابق:</t>
+        </is>
+      </c>
+      <c r="F10" s="153" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="150" t="inlineStr">
+        <is>
+          <t>المعايير والتعليمات</t>
+        </is>
+      </c>
+      <c r="B11" s="150" t="inlineStr">
+        <is>
+          <t>فئات الأجوبة</t>
+        </is>
+      </c>
+      <c r="C11" s="150" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" s="150" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E11" s="150" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F11" s="150" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G11" s="150" t="inlineStr">
+        <is>
+          <t>النتيجة القصوى</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="150" t="inlineStr">
+        <is>
+          <t>2. التقييم الصحي والاجتماعي</t>
+        </is>
+      </c>
+      <c r="G12" s="147" t="inlineStr"/>
+      <c r="H12" s="154" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="150" t="inlineStr">
+        <is>
+          <t>2.1 الوضع الصحي</t>
+        </is>
+      </c>
+      <c r="G13" s="147" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="155" t="inlineStr">
+        <is>
+          <t>2.1.1 عدد الأشخاص المصابين بأمراض مزمنة (السرطان، الربو، أمراض الجهاز التنفسي باستثناء مرضى السكري وضغط الدم)</t>
+        </is>
+      </c>
+      <c r="G14" s="147" t="inlineStr"/>
+      <c r="H14" s="154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="155" t="inlineStr">
+        <is>
+          <t>2.1.2 عدد الأشخاص المصابين بمرض عقلي حاد أو ما شابه ذلك (الحالات المعتمدة)</t>
+        </is>
+      </c>
+      <c r="G15" s="147" t="inlineStr"/>
+      <c r="H15" s="154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="150" t="inlineStr">
+        <is>
+          <t>2.2 الوضع الاجتماعي</t>
+        </is>
+      </c>
+      <c r="G16" s="147" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="155" t="inlineStr">
+        <is>
+          <t>2.2.1 تقييم حالة ضعف الاسرة (رب الأسرة فوق 60/طفل تحت 18/ذوي احتياجات خاصة/امرأة...)</t>
+        </is>
+      </c>
+      <c r="G17" s="147" t="inlineStr"/>
+      <c r="H17" s="154" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="155" t="inlineStr">
+        <is>
+          <t>2.2.2 عدد افراد الاسرة الذين ينامون بغرفة نوم واحدة</t>
+        </is>
+      </c>
+      <c r="G18" s="147" t="inlineStr"/>
+      <c r="H18" s="154" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="155" t="inlineStr">
+        <is>
+          <t>2.2.3 هل يوجد فصل بين الجنسين لعمر فوق 10 سنوات</t>
+        </is>
+      </c>
+      <c r="G19" s="147" t="inlineStr"/>
+      <c r="H19" s="154" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="155" t="inlineStr">
+        <is>
+          <t>2.2.4 هل للأسرة دخل منتظم؟</t>
+        </is>
+      </c>
+      <c r="G20" s="147" t="inlineStr"/>
+      <c r="H20" s="154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="150" t="inlineStr">
+        <is>
+          <t>3. التقييم المادي</t>
+        </is>
+      </c>
+      <c r="G21" s="147" t="inlineStr"/>
+      <c r="H21" s="154" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="155" t="inlineStr">
+        <is>
+          <t>3.1 سلامة هيكل البيت (الانحراف / التكسير / التفلطح / الاستقرار)</t>
+        </is>
+      </c>
+      <c r="C22" s="156" t="inlineStr"/>
+      <c r="D22" s="156" t="inlineStr"/>
+      <c r="E22" s="156" t="inlineStr"/>
+      <c r="F22" s="156" t="inlineStr"/>
+      <c r="G22" s="147" t="inlineStr"/>
+      <c r="H22" s="154" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="150" t="inlineStr">
+        <is>
+          <t>3.2 الظروف الأخرى للبيت (بشكل جزئي)</t>
+        </is>
+      </c>
+      <c r="G23" s="147" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="155" t="inlineStr">
+        <is>
+          <t>3.2.1 حالة المرحاض (النظافة والمساحة)</t>
+        </is>
+      </c>
+      <c r="G24" s="147" t="inlineStr"/>
+      <c r="H24" s="154" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="155" t="inlineStr">
+        <is>
+          <t>3.2.2 حالة المطبخ (النظافة والمساحة)</t>
+        </is>
+      </c>
+      <c r="G25" s="147" t="inlineStr"/>
+      <c r="H25" s="154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="155" t="inlineStr">
+        <is>
+          <t>3.2.3 جودة تهوية المأوى والإضاءة</t>
+        </is>
+      </c>
+      <c r="G26" s="147" t="inlineStr"/>
+      <c r="H26" s="154" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="155" t="inlineStr">
+        <is>
+          <t>3.2.4 مؤشرات الرطوبة في البيت</t>
+        </is>
+      </c>
+      <c r="G27" s="147" t="inlineStr"/>
+      <c r="H27" s="154" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="155" t="inlineStr">
+        <is>
+          <t>3.2.5 طريقة وصل البيت بشبكة الصرف الصحي</t>
+        </is>
+      </c>
+      <c r="G28" s="147" t="inlineStr"/>
+      <c r="H28" s="154" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="157" t="inlineStr">
+        <is>
+          <t>النتيجة الاجمالية النهائية (من 100)</t>
+        </is>
+      </c>
+      <c r="G29" s="158" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="159" t="inlineStr">
+        <is>
+          <t>مصدر البيانات: استمارة تقييم كوبو 2026 — قيم منسوخة تلقائيًا من نسخة مستوردة على هذا الجهاز، بدون أي ربط حي.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B2E9EA7FEDBC2B47B1BB5C1A5E1D6611" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5d390b9e31cab3c913f6315b6da75808">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ae0eac29-bff3-4a8c-bb5e-8697060638a2" xmlns:ns4="bcae0f81-df23-4fab-9ba2-367c4d4a590c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd01a87fa795c8ff6d80afaf1d0f7222" ns3:_="" ns4:_="">

--- a/app/src/main/assets/quantities_template.xlsx
+++ b/app/src/main/assets/quantities_template.xlsx
@@ -22,8 +22,8 @@
     <sheet name="نسبة الإنجاز" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'الكميات  '!$A$2:$J$45</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'الكميات  '!$2:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'الكميات  '!$A$2:$J$45</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'الكميات  '!$2:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/app/src/main/assets/quantities_template.xlsx
+++ b/app/src/main/assets/quantities_template.xlsx
@@ -4278,13 +4278,13 @@
           <t>نموذج تقييم لمنزل السيد/ة</t>
         </is>
       </c>
-      <c r="D1" s="147" t="inlineStr"/>
+      <c r="D1" s="147"/>
       <c r="E1" s="148" t="inlineStr">
         <is>
           <t>المهندس/ة - الباحث/ة الاجتماعي/ة</t>
         </is>
       </c>
-      <c r="G1" s="149" t="inlineStr"/>
+      <c r="G1" s="149"/>
     </row>
     <row r="2">
       <c r="A2" s="150" t="inlineStr">
@@ -4309,13 +4309,13 @@
           <t>عمر رب/ة الاسرة بالسنوات:</t>
         </is>
       </c>
-      <c r="D3" s="153" t="inlineStr"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="151" t="inlineStr">
         <is>
           <t>جنس رب/ة الاسرة:</t>
         </is>
       </c>
-      <c r="F3" s="153" t="inlineStr"/>
+      <c r="F3" s="153"/>
     </row>
     <row r="4">
       <c r="A4" s="151" t="inlineStr">
@@ -4333,13 +4333,13 @@
           <t>الحالة العائلية لرب/ة الاسرة:</t>
         </is>
       </c>
-      <c r="D4" s="153" t="inlineStr"/>
+      <c r="D4" s="153"/>
       <c r="E4" s="151" t="inlineStr">
         <is>
           <t>السكن الحالي:</t>
         </is>
       </c>
-      <c r="F4" s="153" t="inlineStr"/>
+      <c r="F4" s="153"/>
     </row>
     <row r="5">
       <c r="A5" s="151" t="inlineStr">
@@ -4347,13 +4347,13 @@
           <t>اسم رب/ة الاسرة:</t>
         </is>
       </c>
-      <c r="B5" s="153" t="inlineStr"/>
+      <c r="B5" s="153"/>
       <c r="C5" s="151" t="inlineStr">
         <is>
           <t>اذا رب الاسرة متزوج من إمراة ثانية:</t>
         </is>
       </c>
-      <c r="D5" s="153" t="inlineStr"/>
+      <c r="D5" s="153"/>
     </row>
     <row r="6">
       <c r="A6" s="151" t="inlineStr">
@@ -4361,19 +4361,19 @@
           <t>رقم العائلة:</t>
         </is>
       </c>
-      <c r="B6" s="153" t="inlineStr"/>
+      <c r="B6" s="153"/>
       <c r="C6" s="151" t="inlineStr">
         <is>
           <t>وضع ملكية البيت:</t>
         </is>
       </c>
-      <c r="D6" s="153" t="inlineStr"/>
+      <c r="D6" s="153"/>
       <c r="E6" s="151" t="inlineStr">
         <is>
           <t>اوراق الملكية المتوفرة:</t>
         </is>
       </c>
-      <c r="F6" s="153" t="inlineStr"/>
+      <c r="F6" s="153"/>
     </row>
     <row r="7">
       <c r="A7" s="151" t="inlineStr">
@@ -4381,13 +4381,13 @@
           <t>رقم التسجيل في الكرت الابيض لرب العائلة:</t>
         </is>
       </c>
-      <c r="B7" s="153" t="inlineStr"/>
+      <c r="B7" s="153"/>
       <c r="C7" s="151" t="inlineStr">
         <is>
           <t>رقم تعريف قطعة الأرض:</t>
         </is>
       </c>
-      <c r="D7" s="153" t="inlineStr"/>
+      <c r="D7" s="153"/>
       <c r="E7" s="151" t="inlineStr">
         <is>
           <t>العنوان:</t>
@@ -4405,19 +4405,19 @@
           <t>رقم السجل/ رقم الليدجر:</t>
         </is>
       </c>
-      <c r="B8" s="153" t="inlineStr"/>
+      <c r="B8" s="153"/>
       <c r="C8" s="151" t="inlineStr">
         <is>
           <t>رقم المسكن:</t>
         </is>
       </c>
-      <c r="D8" s="153" t="inlineStr"/>
+      <c r="D8" s="153"/>
       <c r="E8" s="151" t="inlineStr">
         <is>
           <t>اسم الشارع:</t>
         </is>
       </c>
-      <c r="F8" s="153" t="inlineStr"/>
+      <c r="F8" s="153"/>
     </row>
     <row r="9">
       <c r="A9" s="151" t="inlineStr">
@@ -4425,19 +4425,19 @@
           <t>عدد افراد الاسرة المسجلين:</t>
         </is>
       </c>
-      <c r="B9" s="153" t="inlineStr"/>
+      <c r="B9" s="153"/>
       <c r="C9" s="151" t="inlineStr">
         <is>
           <t>رقم الجوال 1:</t>
         </is>
       </c>
-      <c r="D9" s="153" t="inlineStr"/>
+      <c r="D9" s="153"/>
       <c r="E9" s="151" t="inlineStr">
         <is>
           <t>عنوان المنزل:</t>
         </is>
       </c>
-      <c r="F9" s="153" t="inlineStr"/>
+      <c r="F9" s="153"/>
     </row>
     <row r="10">
       <c r="A10" s="151" t="inlineStr">
@@ -4445,19 +4445,19 @@
           <t>رقم الهوية الوطني ل رب/ة الاسرة:</t>
         </is>
       </c>
-      <c r="B10" s="153" t="inlineStr"/>
+      <c r="B10" s="153"/>
       <c r="C10" s="151" t="inlineStr">
         <is>
           <t>رقم الجوال 2:</t>
         </is>
       </c>
-      <c r="D10" s="153" t="inlineStr"/>
+      <c r="D10" s="153"/>
       <c r="E10" s="151" t="inlineStr">
         <is>
           <t>الطابق:</t>
         </is>
       </c>
-      <c r="F10" s="153" t="inlineStr"/>
+      <c r="F10" s="153"/>
     </row>
     <row r="11">
       <c r="A11" s="150" t="inlineStr">
@@ -4502,7 +4502,7 @@
           <t>2. التقييم الصحي والاجتماعي</t>
         </is>
       </c>
-      <c r="G12" s="147" t="inlineStr"/>
+      <c r="G12" s="147"/>
       <c r="H12" s="154" t="n">
         <v>40</v>
       </c>
@@ -4513,7 +4513,7 @@
           <t>2.1 الوضع الصحي</t>
         </is>
       </c>
-      <c r="G13" s="147" t="inlineStr"/>
+      <c r="G13" s="147"/>
     </row>
     <row r="14">
       <c r="A14" s="155" t="inlineStr">
@@ -4521,7 +4521,7 @@
           <t>2.1.1 عدد الأشخاص المصابين بأمراض مزمنة (السرطان، الربو، أمراض الجهاز التنفسي باستثناء مرضى السكري وضغط الدم)</t>
         </is>
       </c>
-      <c r="G14" s="147" t="inlineStr"/>
+      <c r="G14" s="147"/>
       <c r="H14" s="154" t="n">
         <v>4</v>
       </c>
@@ -4532,7 +4532,7 @@
           <t>2.1.2 عدد الأشخاص المصابين بمرض عقلي حاد أو ما شابه ذلك (الحالات المعتمدة)</t>
         </is>
       </c>
-      <c r="G15" s="147" t="inlineStr"/>
+      <c r="G15" s="147"/>
       <c r="H15" s="154" t="n">
         <v>4</v>
       </c>
@@ -4543,7 +4543,7 @@
           <t>2.2 الوضع الاجتماعي</t>
         </is>
       </c>
-      <c r="G16" s="147" t="inlineStr"/>
+      <c r="G16" s="147"/>
     </row>
     <row r="17">
       <c r="A17" s="155" t="inlineStr">
@@ -4551,7 +4551,7 @@
           <t>2.2.1 تقييم حالة ضعف الاسرة (رب الأسرة فوق 60/طفل تحت 18/ذوي احتياجات خاصة/امرأة...)</t>
         </is>
       </c>
-      <c r="G17" s="147" t="inlineStr"/>
+      <c r="G17" s="147"/>
       <c r="H17" s="154" t="n">
         <v>8</v>
       </c>
@@ -4562,7 +4562,7 @@
           <t>2.2.2 عدد افراد الاسرة الذين ينامون بغرفة نوم واحدة</t>
         </is>
       </c>
-      <c r="G18" s="147" t="inlineStr"/>
+      <c r="G18" s="147"/>
       <c r="H18" s="154" t="n">
         <v>6</v>
       </c>
@@ -4573,7 +4573,7 @@
           <t>2.2.3 هل يوجد فصل بين الجنسين لعمر فوق 10 سنوات</t>
         </is>
       </c>
-      <c r="G19" s="147" t="inlineStr"/>
+      <c r="G19" s="147"/>
       <c r="H19" s="154" t="n">
         <v>5</v>
       </c>
@@ -4584,7 +4584,7 @@
           <t>2.2.4 هل للأسرة دخل منتظم؟</t>
         </is>
       </c>
-      <c r="G20" s="147" t="inlineStr"/>
+      <c r="G20" s="147"/>
       <c r="H20" s="154" t="n">
         <v>4</v>
       </c>
@@ -4595,7 +4595,7 @@
           <t>3. التقييم المادي</t>
         </is>
       </c>
-      <c r="G21" s="147" t="inlineStr"/>
+      <c r="G21" s="147"/>
       <c r="H21" s="154" t="n">
         <v>60</v>
       </c>
@@ -4606,11 +4606,11 @@
           <t>3.1 سلامة هيكل البيت (الانحراف / التكسير / التفلطح / الاستقرار)</t>
         </is>
       </c>
-      <c r="C22" s="156" t="inlineStr"/>
-      <c r="D22" s="156" t="inlineStr"/>
-      <c r="E22" s="156" t="inlineStr"/>
-      <c r="F22" s="156" t="inlineStr"/>
-      <c r="G22" s="147" t="inlineStr"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="156"/>
+      <c r="G22" s="147"/>
       <c r="H22" s="154" t="n">
         <v>40</v>
       </c>
@@ -4621,7 +4621,7 @@
           <t>3.2 الظروف الأخرى للبيت (بشكل جزئي)</t>
         </is>
       </c>
-      <c r="G23" s="147" t="inlineStr"/>
+      <c r="G23" s="147"/>
     </row>
     <row r="24">
       <c r="A24" s="155" t="inlineStr">
@@ -4629,7 +4629,7 @@
           <t>3.2.1 حالة المرحاض (النظافة والمساحة)</t>
         </is>
       </c>
-      <c r="G24" s="147" t="inlineStr"/>
+      <c r="G24" s="147"/>
       <c r="H24" s="154" t="n">
         <v>5</v>
       </c>
@@ -4640,7 +4640,7 @@
           <t>3.2.2 حالة المطبخ (النظافة والمساحة)</t>
         </is>
       </c>
-      <c r="G25" s="147" t="inlineStr"/>
+      <c r="G25" s="147"/>
       <c r="H25" s="154" t="n">
         <v>4</v>
       </c>
@@ -4651,7 +4651,7 @@
           <t>3.2.3 جودة تهوية المأوى والإضاءة</t>
         </is>
       </c>
-      <c r="G26" s="147" t="inlineStr"/>
+      <c r="G26" s="147"/>
       <c r="H26" s="154" t="n">
         <v>8</v>
       </c>
@@ -4662,7 +4662,7 @@
           <t>3.2.4 مؤشرات الرطوبة في البيت</t>
         </is>
       </c>
-      <c r="G27" s="147" t="inlineStr"/>
+      <c r="G27" s="147"/>
       <c r="H27" s="154" t="n">
         <v>8</v>
       </c>
@@ -4673,7 +4673,7 @@
           <t>3.2.5 طريقة وصل البيت بشبكة الصرف الصحي</t>
         </is>
       </c>
-      <c r="G28" s="147" t="inlineStr"/>
+      <c r="G28" s="147"/>
       <c r="H28" s="154" t="n">
         <v>5</v>
       </c>
@@ -4684,7 +4684,7 @@
           <t>النتيجة الاجمالية النهائية (من 100)</t>
         </is>
       </c>
-      <c r="G29" s="158" t="inlineStr"/>
+      <c r="G29" s="158"/>
     </row>
     <row r="30">
       <c r="A30" s="159" t="inlineStr">

--- a/app/src/main/assets/quantities_template.xlsx
+++ b/app/src/main/assets/quantities_template.xlsx
@@ -24,8 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="29">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -193,32 +195,91 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
+      <color theme="1"/>
       <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -305,16 +366,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF6D9"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE9EF"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="75">
+  <borders count="143">
     <border>
       <left/>
       <right/>
@@ -1208,48 +1283,894 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="3" tint="0.499984740745262"/>
+      </right>
+      <top style="thick">
+        <color theme="3" tint="0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00999999"/>
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.3499862666707358"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1257,10 +2178,41 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00999999"/>
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1272,7 +2224,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
@@ -1701,48 +2653,371 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="71" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="72" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="93" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="16" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
@@ -2074,492 +3349,1121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="32.3984375" customWidth="1" min="2" max="2"/>
+    <col width="28.8984375" customWidth="1" min="3" max="3"/>
+    <col width="26.69921875" customWidth="1" min="4" max="4"/>
+    <col width="20.59765625" customWidth="1" min="5" max="5"/>
+    <col width="19.3984375" customWidth="1" min="6" max="6"/>
+    <col width="16.59765625" customWidth="1" min="7" max="7"/>
+    <col width="23.3984375" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="145" t="inlineStr">
         <is>
-          <t>نموذج تقييم لمنزل السيد/ة</t>
+          <t xml:space="preserve">نموذج تقييم لمنزل السيد/ة </t>
         </is>
       </c>
       <c r="B1" s="146" t="n"/>
       <c r="C1" s="147" t="n"/>
-      <c r="D1" s="148" t="n"/>
+      <c r="D1" s="148" t="inlineStr">
+        <is>
+          <t>بشار العطية</t>
+        </is>
+      </c>
       <c r="E1" s="149" t="inlineStr">
         <is>
-          <t>المهندس/ة - الباحث/ة الاجتماعي/ة</t>
-        </is>
-      </c>
-      <c r="F1" s="147" t="n"/>
-      <c r="G1" s="150" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="151" t="inlineStr">
+          <t>مريم ابو عطوان</t>
+        </is>
+      </c>
+      <c r="F1" s="149" t="n">
+        <v>46047.55154947917</v>
+      </c>
+      <c r="G1" s="150" t="inlineStr">
+        <is>
+          <t>زيارة الترميم</t>
+        </is>
+      </c>
+      <c r="H1" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        /                /2026</t>
+        </is>
+      </c>
+      <c r="J1" s="151" t="n"/>
+    </row>
+    <row r="2" ht="16.2" customHeight="1">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>1. معلومات عامة</t>
         </is>
       </c>
-      <c r="B2" s="146" t="n"/>
-      <c r="C2" s="146" t="n"/>
-      <c r="D2" s="146" t="n"/>
-      <c r="E2" s="146" t="n"/>
-      <c r="F2" s="146" t="n"/>
+      <c r="B2" s="153" t="n"/>
+      <c r="C2" s="153" t="n"/>
+      <c r="D2" s="153" t="n"/>
+      <c r="E2" s="153" t="n"/>
+      <c r="F2" s="154" t="n"/>
       <c r="G2" s="147" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="152" t="inlineStr">
+      <c r="H2" s="155" t="n"/>
+    </row>
+    <row r="3" ht="17.4" customHeight="1">
+      <c r="A3" s="156" t="inlineStr">
         <is>
           <t>البلد:</t>
         </is>
       </c>
-      <c r="B3" s="153" t="inlineStr">
+      <c r="B3" s="157" t="inlineStr">
         <is>
           <t>Syria</t>
         </is>
       </c>
-      <c r="C3" s="152" t="inlineStr">
-        <is>
-          <t>عمر رب/ة الاسرة بالسنوات:</t>
-        </is>
-      </c>
-      <c r="D3" s="154" t="n"/>
-      <c r="E3" s="152" t="inlineStr">
-        <is>
-          <t>جنس رب/ة الاسرة:</t>
-        </is>
-      </c>
-      <c r="F3" s="154" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="152" t="inlineStr">
+      <c r="C3" s="158" t="inlineStr">
+        <is>
+          <t>عمر رب الاسرة:</t>
+        </is>
+      </c>
+      <c r="D3" s="159" t="n"/>
+      <c r="E3" s="160" t="inlineStr">
+        <is>
+          <t>جنس رب الاسرة</t>
+        </is>
+      </c>
+      <c r="F3" s="161" t="n"/>
+      <c r="G3" s="161" t="n"/>
+      <c r="H3" s="162" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="163" t="inlineStr">
         <is>
           <t>المخيم:</t>
         </is>
       </c>
-      <c r="B4" s="153" t="inlineStr">
+      <c r="B4" s="164" t="inlineStr">
         <is>
           <t>Yarmouk</t>
         </is>
       </c>
-      <c r="C4" s="152" t="inlineStr">
-        <is>
-          <t>الحالة العائلية لرب/ة الاسرة:</t>
-        </is>
-      </c>
-      <c r="D4" s="154" t="n"/>
-      <c r="E4" s="152" t="inlineStr">
-        <is>
-          <t>السكن الحالي:</t>
-        </is>
-      </c>
-      <c r="F4" s="154" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="152" t="inlineStr">
-        <is>
-          <t>اسم رب/ة الاسرة:</t>
-        </is>
-      </c>
-      <c r="B5" s="154" t="n"/>
-      <c r="C5" s="152" t="inlineStr">
-        <is>
-          <t>اذا رب الاسرة متزوج من إمراة ثانية:</t>
-        </is>
-      </c>
-      <c r="D5" s="154" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="152" t="inlineStr">
-        <is>
-          <t>رقم العائلة:</t>
-        </is>
-      </c>
-      <c r="B6" s="154" t="n"/>
-      <c r="C6" s="152" t="inlineStr">
-        <is>
-          <t>وضع ملكية البيت:</t>
-        </is>
-      </c>
-      <c r="D6" s="154" t="n"/>
-      <c r="E6" s="152" t="inlineStr">
-        <is>
-          <t>اوراق الملكية المتوفرة:</t>
-        </is>
-      </c>
-      <c r="F6" s="154" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="152" t="inlineStr">
-        <is>
-          <t>رقم التسجيل في الكرت الابيض لرب العائلة:</t>
-        </is>
-      </c>
-      <c r="B7" s="154" t="n"/>
-      <c r="C7" s="152" t="inlineStr">
-        <is>
-          <t>رقم تعريف قطعة الأرض:</t>
-        </is>
-      </c>
-      <c r="D7" s="154" t="n"/>
-      <c r="E7" s="152" t="inlineStr">
-        <is>
-          <t>العنوان:</t>
-        </is>
-      </c>
-      <c r="F7" s="153" t="inlineStr">
-        <is>
-          <t>مخيم اليرموك</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="152" t="inlineStr">
-        <is>
-          <t>رقم السجل/ رقم الليدجر:</t>
-        </is>
-      </c>
-      <c r="B8" s="154" t="n"/>
-      <c r="C8" s="152" t="inlineStr">
-        <is>
-          <t>رقم المسكن:</t>
-        </is>
-      </c>
-      <c r="D8" s="154" t="n"/>
-      <c r="E8" s="152" t="inlineStr">
-        <is>
-          <t>اسم الشارع:</t>
-        </is>
-      </c>
-      <c r="F8" s="154" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="152" t="inlineStr">
-        <is>
-          <t>عدد افراد الاسرة المسجلين:</t>
-        </is>
-      </c>
-      <c r="B9" s="154" t="n"/>
-      <c r="C9" s="152" t="inlineStr">
-        <is>
-          <t>رقم الجوال 1:</t>
-        </is>
-      </c>
-      <c r="D9" s="154" t="n"/>
-      <c r="E9" s="152" t="inlineStr">
-        <is>
-          <t>عنوان المنزل:</t>
-        </is>
-      </c>
-      <c r="F9" s="154" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="152" t="inlineStr">
-        <is>
-          <t>رقم الهوية الوطني ل رب/ة الاسرة:</t>
-        </is>
-      </c>
-      <c r="B10" s="154" t="n"/>
-      <c r="C10" s="152" t="inlineStr">
-        <is>
-          <t>رقم الجوال 2:</t>
-        </is>
-      </c>
-      <c r="D10" s="154" t="n"/>
-      <c r="E10" s="152" t="inlineStr">
-        <is>
-          <t>الطابق:</t>
-        </is>
-      </c>
-      <c r="F10" s="154" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="151" t="inlineStr">
-        <is>
-          <t>المعايير والتعليمات</t>
-        </is>
-      </c>
-      <c r="B11" s="151" t="inlineStr">
-        <is>
-          <t>فئات الأجوبة</t>
-        </is>
-      </c>
-      <c r="C11" s="151" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D11" s="151" t="inlineStr">
+      <c r="C4" s="165" t="inlineStr">
+        <is>
+          <t>الحالة العائلية لرب الاسرة</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="n"/>
+      <c r="E4" s="167" t="inlineStr">
+        <is>
+          <t>السكن الحالي</t>
+        </is>
+      </c>
+      <c r="F4" s="168" t="n"/>
+      <c r="G4" s="169" t="inlineStr">
+        <is>
+          <t>عدد الاسر في المنزل</t>
+        </is>
+      </c>
+      <c r="H4" s="170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="17.4" customHeight="1">
+      <c r="A5" s="163" t="inlineStr">
+        <is>
+          <t>اسم رب الاسرة:</t>
+        </is>
+      </c>
+      <c r="B5" s="164" t="n"/>
+      <c r="C5" s="163" t="inlineStr">
+        <is>
+          <t>اذا رب الاسرة متزوج من إمراة ثانية</t>
+        </is>
+      </c>
+      <c r="D5" s="164" t="n"/>
+      <c r="E5" s="171" t="n"/>
+      <c r="F5" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يسكنون نفس البيت </t>
+        </is>
+      </c>
+      <c r="G5" s="172" t="inlineStr">
+        <is>
+          <t>يسكنون في بيت منفصل</t>
+        </is>
+      </c>
+      <c r="H5" s="173" t="inlineStr">
+        <is>
+          <t>يسكنون خارج المخيم</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17.4" customHeight="1">
+      <c r="A6" s="163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقم العائلة: </t>
+        </is>
+      </c>
+      <c r="B6" s="164" t="n"/>
+      <c r="C6" s="165" t="inlineStr">
+        <is>
+          <t>وضع ملكية البيت</t>
+        </is>
+      </c>
+      <c r="D6" s="164" t="n"/>
+      <c r="E6" s="174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="175" t="inlineStr">
+        <is>
+          <t>ملكية البيت مشتركة/ خاصة</t>
+        </is>
+      </c>
+      <c r="G6" s="175" t="inlineStr">
+        <is>
+          <t>بدون مقابل مادي</t>
+        </is>
+      </c>
+      <c r="H6" s="176" t="inlineStr">
+        <is>
+          <t>إيجار</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقم التسجيل في الكرت الابيض لرب العائلة: </t>
+        </is>
+      </c>
+      <c r="B7" s="164" t="n"/>
+      <c r="C7" s="165" t="inlineStr">
+        <is>
+          <t>رقم تعريف قطعة الأرض</t>
+        </is>
+      </c>
+      <c r="D7" s="164" t="n"/>
+      <c r="E7" s="177" t="n"/>
+      <c r="F7" s="178" t="n"/>
+      <c r="G7" s="178" t="n"/>
+      <c r="H7" s="179" t="n"/>
+    </row>
+    <row r="8" ht="19.95" customHeight="1">
+      <c r="A8" s="163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقم السجل/ رقم الشخص </t>
+        </is>
+      </c>
+      <c r="B8" s="164" t="n"/>
+      <c r="C8" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقم المسكن </t>
+        </is>
+      </c>
+      <c r="D8" s="164" t="n"/>
+      <c r="E8" s="180" t="inlineStr">
+        <is>
+          <t>اسم الشارع</t>
+        </is>
+      </c>
+      <c r="F8" s="181" t="n"/>
+      <c r="G8" s="182" t="n"/>
+      <c r="H8" s="183" t="n"/>
+    </row>
+    <row r="9" ht="40.95" customHeight="1">
+      <c r="A9" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدد افراد الاسرة المسجلين </t>
+        </is>
+      </c>
+      <c r="B9" s="185" t="n"/>
+      <c r="C9" s="186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقم التلفون </t>
+        </is>
+      </c>
+      <c r="D9" s="187" t="n"/>
+      <c r="E9" s="188" t="inlineStr">
+        <is>
+          <t>عنوان المنزل</t>
+        </is>
+      </c>
+      <c r="F9" s="189" t="n"/>
+      <c r="H9" s="190" t="n"/>
+    </row>
+    <row r="10" ht="21.6" customHeight="1">
+      <c r="A10" s="191" t="inlineStr">
+        <is>
+          <t>رقم الهوية الوطني:</t>
+        </is>
+      </c>
+      <c r="B10" s="192" t="n"/>
+      <c r="C10" s="193" t="n"/>
+      <c r="D10" s="194" t="n"/>
+      <c r="E10" s="195" t="inlineStr">
+        <is>
+          <t>الطابق</t>
+        </is>
+      </c>
+      <c r="F10" s="196" t="inlineStr">
+        <is>
+          <t>بناء طابقي ( شقة سكنية)</t>
+        </is>
+      </c>
+      <c r="G10" s="197" t="n"/>
+      <c r="H10" s="198" t="n"/>
+    </row>
+    <row r="11" ht="16.2" customHeight="1">
+      <c r="A11" s="199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المعايير والتعليمات </t>
+        </is>
+      </c>
+      <c r="B11" s="200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فئات الأجوبة </t>
+        </is>
+      </c>
+      <c r="C11" s="201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A </t>
+        </is>
+      </c>
+      <c r="D11" s="201" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E11" s="151" t="inlineStr">
+      <c r="E11" s="201" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F11" s="151" t="inlineStr">
+      <c r="F11" s="201" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G11" s="151" t="inlineStr">
-        <is>
-          <t>النتيجة القصوى</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="151" t="inlineStr">
+      <c r="G11" s="202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النتيجة القصوى </t>
+        </is>
+      </c>
+      <c r="H11" s="155" t="n"/>
+    </row>
+    <row r="12" ht="21.6" customHeight="1">
+      <c r="A12" s="203" t="inlineStr">
         <is>
           <t>2. التقييم الصحي والاجتماعي</t>
         </is>
       </c>
-      <c r="B12" s="146" t="n"/>
-      <c r="C12" s="146" t="n"/>
-      <c r="D12" s="146" t="n"/>
-      <c r="E12" s="146" t="n"/>
-      <c r="F12" s="147" t="n"/>
-      <c r="G12" s="148" t="n"/>
-      <c r="H12" s="155" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="151" t="inlineStr">
-        <is>
-          <t>2.1 الوضع الصحي</t>
-        </is>
-      </c>
-      <c r="B13" s="146" t="n"/>
-      <c r="C13" s="146" t="n"/>
-      <c r="D13" s="146" t="n"/>
-      <c r="E13" s="146" t="n"/>
-      <c r="F13" s="147" t="n"/>
-      <c r="G13" s="148" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="156" t="inlineStr">
-        <is>
-          <t>2.1.1 عدد الأشخاص المصابين بأمراض مزمنة (السرطان، الربو، أمراض الجهاز التنفسي باستثناء مرضى السكري وضغط الدم)</t>
-        </is>
-      </c>
-      <c r="G14" s="148" t="n"/>
-      <c r="H14" s="155" t="n">
+      <c r="B12" s="147" t="n"/>
+      <c r="C12" s="147" t="n"/>
+      <c r="D12" s="147" t="n"/>
+      <c r="E12" s="147" t="n"/>
+      <c r="F12" s="155" t="n"/>
+      <c r="G12" s="204" t="n"/>
+      <c r="H12" s="155" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1 الوضع الصحي </t>
+        </is>
+      </c>
+      <c r="B13" s="206" t="n"/>
+      <c r="C13" s="206" t="n"/>
+      <c r="D13" s="206" t="n"/>
+      <c r="E13" s="206" t="n"/>
+      <c r="F13" s="207" t="n"/>
+      <c r="G13" s="208" t="n"/>
+      <c r="H13" s="209" t="n"/>
+    </row>
+    <row r="14" ht="15.6" customHeight="1">
+      <c r="A14" s="210" t="inlineStr">
+        <is>
+          <t>2.1.1 عدد الأشخاص المصابين بأمراض مزمنة
+(السرطان، الربو، أمراض الجهاز التنفسي باستثناء مرضى السكري وضغط الدم)</t>
+        </is>
+      </c>
+      <c r="B14" s="211" t="n"/>
+      <c r="C14" s="212" t="inlineStr">
+        <is>
+          <t>≥ 3</t>
+        </is>
+      </c>
+      <c r="D14" s="213" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="214" t="n"/>
+      <c r="H14" s="215" t="n"/>
+    </row>
+    <row r="15" ht="15.6" customHeight="1">
+      <c r="A15" s="216" t="n"/>
+      <c r="B15" s="217" t="n"/>
+      <c r="C15" s="218" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="218" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="219" t="n"/>
+      <c r="H15" s="220" t="n"/>
+    </row>
+    <row r="16" ht="15.6" customHeight="1">
+      <c r="A16" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2.1.2عدد الأشخاص المصابين بمرض عقلي حاد أو ما شابه ذلك 
+(الحالات المعتمدة)</t>
+        </is>
+      </c>
+      <c r="B16" s="222" t="n"/>
+      <c r="C16" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نعم </t>
+        </is>
+      </c>
+      <c r="D16" s="224" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="E16" s="224" t="n"/>
+      <c r="F16" s="223" t="n"/>
+      <c r="G16" s="225" t="n"/>
+      <c r="H16" s="215" t="n"/>
+    </row>
+    <row r="17" ht="16.2" customHeight="1">
+      <c r="A17" s="210" t="n"/>
+      <c r="B17" s="211" t="n"/>
+      <c r="C17" s="226" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="156" t="inlineStr">
-        <is>
-          <t>2.1.2 عدد الأشخاص المصابين بمرض عقلي حاد أو ما شابه ذلك (الحالات المعتمدة)</t>
-        </is>
-      </c>
-      <c r="G15" s="148" t="n"/>
-      <c r="H15" s="155" t="n">
+      <c r="D17" s="226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="227" t="n"/>
+      <c r="F17" s="227" t="n"/>
+      <c r="G17" s="228" t="n"/>
+      <c r="H17" s="229" t="n"/>
+    </row>
+    <row r="18" ht="21.6" customHeight="1">
+      <c r="A18" s="230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 الوضع الاجتماعي </t>
+        </is>
+      </c>
+      <c r="B18" s="147" t="n"/>
+      <c r="C18" s="147" t="n"/>
+      <c r="D18" s="147" t="n"/>
+      <c r="E18" s="147" t="n"/>
+      <c r="F18" s="231" t="n"/>
+      <c r="G18" s="208" t="n"/>
+      <c r="H18" s="209" t="n"/>
+    </row>
+    <row r="19" ht="31.2" customHeight="1">
+      <c r="A19" s="232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           2.2.1  تقييم حالة ضعف الاسرة             
+     1-رب العائلة فوق عمر الستين   2 - رب العائلة طفل تحت18عاما    
+       3-  رب العائلة شخص من ذوي الاحتياجات الخاصة         
+   4- يوجد في العائلة شخصين أو أكثر من من ذوي الاحتياجات الخاصة 5-  رب العائلة امرأة </t>
+        </is>
+      </c>
+      <c r="B19" s="233" t="n"/>
+      <c r="C19" s="234" t="inlineStr">
+        <is>
+          <t>يستوفي ثلاثة  معايير للضعف أو أسرة يرأسها طفل</t>
+        </is>
+      </c>
+      <c r="D19" s="235" t="inlineStr">
+        <is>
+          <t>يستوفي اثنان من معايير للضعف</t>
+        </is>
+      </c>
+      <c r="E19" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يستوفي أحد معايير الضعف </t>
+        </is>
+      </c>
+      <c r="F19" s="236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا يستوفي أي من معايير الضعف </t>
+        </is>
+      </c>
+      <c r="G19" s="237" t="n"/>
+      <c r="H19" s="215" t="n"/>
+    </row>
+    <row r="20" ht="31.95" customHeight="1">
+      <c r="A20" s="238" t="n"/>
+      <c r="B20" s="239" t="n"/>
+      <c r="C20" s="240" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="240" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="240" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="242" t="n"/>
+      <c r="H20" s="220" t="n"/>
+    </row>
+    <row r="21" ht="15.6" customHeight="1">
+      <c r="A21" s="232" t="inlineStr">
+        <is>
+          <t>2.2.2 عدد افراد الاسرة الذي يعيشون في البيت وينامون بغرفة نوم واحدة
+(بما في ذلك الاسرة الممتدة الذين يعيشون مع الاسرة بشكل دائم)</t>
+        </is>
+      </c>
+      <c r="B21" s="233" t="n"/>
+      <c r="C21" s="243" t="inlineStr">
+        <is>
+          <t>≥ 7</t>
+        </is>
+      </c>
+      <c r="D21" s="244" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="E21" s="244" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="F21" s="245" t="inlineStr">
+        <is>
+          <t>≤ 2</t>
+        </is>
+      </c>
+      <c r="G21" s="237" t="n"/>
+      <c r="H21" s="215" t="n"/>
+    </row>
+    <row r="22" ht="16.2" customHeight="1">
+      <c r="A22" s="238" t="n"/>
+      <c r="B22" s="239" t="n"/>
+      <c r="C22" s="246" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="246" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="151" t="inlineStr">
-        <is>
-          <t>2.2 الوضع الاجتماعي</t>
-        </is>
-      </c>
-      <c r="B16" s="146" t="n"/>
-      <c r="C16" s="146" t="n"/>
-      <c r="D16" s="146" t="n"/>
-      <c r="E16" s="146" t="n"/>
-      <c r="F16" s="147" t="n"/>
-      <c r="G16" s="148" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="156" t="inlineStr">
-        <is>
-          <t>2.2.1 تقييم حالة ضعف الاسرة (رب الأسرة فوق 60/طفل تحت 18/ذوي احتياجات خاصة/امرأة...)</t>
-        </is>
-      </c>
-      <c r="G17" s="148" t="n"/>
-      <c r="H17" s="155" t="n">
+      <c r="E22" s="246" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="242" t="n"/>
+      <c r="H22" s="220" t="n"/>
+    </row>
+    <row r="23" ht="18.6" customHeight="1">
+      <c r="A23" s="247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.3 هل يوجد فصل بين الجنسين لعمرفوق 10 سنوات
+(شخصين أو أكثر أعمارهم فوق 10 سنوات من جنسين مختلفين يقيمون في نفس غرفة النوم </t>
+        </is>
+      </c>
+      <c r="B23" s="233" t="n"/>
+      <c r="C23" s="243" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="D23" s="244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نعم </t>
+        </is>
+      </c>
+      <c r="E23" s="244" t="n"/>
+      <c r="F23" s="245" t="n"/>
+      <c r="G23" s="237" t="n"/>
+      <c r="H23" s="215" t="n"/>
+    </row>
+    <row r="24" ht="19.2" customHeight="1">
+      <c r="A24" s="238" t="n"/>
+      <c r="B24" s="239" t="n"/>
+      <c r="C24" s="246" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="248" t="n"/>
+      <c r="F24" s="249" t="n"/>
+      <c r="G24" s="242" t="n"/>
+      <c r="H24" s="220" t="n"/>
+    </row>
+    <row r="25" ht="14.4" customHeight="1">
+      <c r="A25" s="232" t="inlineStr">
+        <is>
+          <t>2.2.4 هل للأسرة دخل منتظم؟</t>
+        </is>
+      </c>
+      <c r="B25" s="233" t="n"/>
+      <c r="C25" s="243" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="D25" s="244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نعم </t>
+        </is>
+      </c>
+      <c r="E25" s="244" t="n"/>
+      <c r="F25" s="245" t="n"/>
+      <c r="G25" s="250" t="n"/>
+      <c r="H25" s="215" t="n"/>
+    </row>
+    <row r="26" ht="18.9" customHeight="1">
+      <c r="A26" s="238" t="n"/>
+      <c r="B26" s="239" t="n"/>
+      <c r="C26" s="246" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="248" t="n"/>
+      <c r="F26" s="249" t="n"/>
+      <c r="G26" s="238" t="n"/>
+      <c r="H26" s="229" t="n"/>
+    </row>
+    <row r="27" ht="22.95" customHeight="1">
+      <c r="A27" s="203" t="inlineStr">
+        <is>
+          <t>3.  التقييم المادي</t>
+        </is>
+      </c>
+      <c r="B27" s="147" t="n"/>
+      <c r="C27" s="147" t="n"/>
+      <c r="D27" s="147" t="n"/>
+      <c r="E27" s="147" t="n"/>
+      <c r="F27" s="155" t="n"/>
+      <c r="G27" s="204" t="n"/>
+      <c r="H27" s="155" t="n"/>
+    </row>
+    <row r="28" ht="16.2" customHeight="1">
+      <c r="A28" s="251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1 سلامة هيكل البيت </t>
+        </is>
+      </c>
+      <c r="B28" s="233" t="n"/>
+      <c r="C28" s="252" t="inlineStr">
+        <is>
+          <t>الانحراف</t>
+        </is>
+      </c>
+      <c r="D28" s="252" t="inlineStr">
+        <is>
+          <t>التكسير</t>
+        </is>
+      </c>
+      <c r="E28" s="252" t="inlineStr">
+        <is>
+          <t>التفلطح</t>
+        </is>
+      </c>
+      <c r="F28" s="253" t="inlineStr">
+        <is>
+          <t>الاستقرار</t>
+        </is>
+      </c>
+      <c r="G28" s="254" t="n"/>
+      <c r="H28" s="183" t="n"/>
+    </row>
+    <row r="29" ht="21.9" customHeight="1">
+      <c r="A29" s="255" t="n"/>
+      <c r="B29" s="256" t="n"/>
+      <c r="C29" s="257" t="inlineStr">
+        <is>
+          <t>0-10-15</t>
+        </is>
+      </c>
+      <c r="D29" s="257" t="inlineStr">
+        <is>
+          <t>0-7-10</t>
+        </is>
+      </c>
+      <c r="E29" s="257" t="inlineStr">
+        <is>
+          <t>0-3-5</t>
+        </is>
+      </c>
+      <c r="F29" s="257" t="inlineStr">
+        <is>
+          <t>0-7-10</t>
+        </is>
+      </c>
+      <c r="G29" s="258" t="n"/>
+      <c r="H29" s="190" t="n"/>
+    </row>
+    <row r="30" ht="16.2" customHeight="1">
+      <c r="A30" s="238" t="n"/>
+      <c r="B30" s="239" t="n"/>
+      <c r="C30" s="259" t="n"/>
+      <c r="D30" s="259" t="n"/>
+      <c r="E30" s="259" t="n"/>
+      <c r="F30" s="259" t="n"/>
+      <c r="G30" s="228" t="n"/>
+      <c r="H30" s="229" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="260" t="inlineStr">
+        <is>
+          <t>3.2الظروف الأخرى للبيت ( بشكل جزئي)</t>
+        </is>
+      </c>
+      <c r="B31" s="206" t="n"/>
+      <c r="C31" s="206" t="n"/>
+      <c r="D31" s="206" t="n"/>
+      <c r="E31" s="206" t="n"/>
+      <c r="F31" s="207" t="n"/>
+      <c r="G31" s="208" t="n"/>
+      <c r="H31" s="209" t="n"/>
+      <c r="I31" s="261" t="n"/>
+    </row>
+    <row r="32" ht="35.4" customHeight="1">
+      <c r="A32" s="262" t="inlineStr">
+        <is>
+          <t>3.2.1ما هي حالة المرحاض في البيت ؟ بما في ذلك مرحاض مخصص للأشخاص من ذوي الاحتياجات الخاصة؟ 
+(الحد الأدنى لمساحة المرحاض 2 م2)</t>
+        </is>
+      </c>
+      <c r="B32" s="263" t="n"/>
+      <c r="C32" s="264" t="inlineStr">
+        <is>
+          <t>حالة جيد وقياس جيد
+(المساحة ≥ 2امتر مكعب)</t>
+        </is>
+      </c>
+      <c r="D32" s="264" t="inlineStr">
+        <is>
+          <t>حالة جيد وقياس سيء
+(المساحة ≥ 2امتر مكعب)</t>
+        </is>
+      </c>
+      <c r="E32" s="265" t="inlineStr">
+        <is>
+          <t>حالة سيئة وقياس جيد
+(المساحة ≥ 2امتر مكعب)</t>
+        </is>
+      </c>
+      <c r="F32" s="265" t="inlineStr">
+        <is>
+          <t>حالة سيئة وقياس سيء
+(المساحة ˂ 2امتر مكعب)</t>
+        </is>
+      </c>
+      <c r="G32" s="214" t="n"/>
+      <c r="H32" s="215" t="n"/>
+    </row>
+    <row r="33" ht="15.6" customHeight="1">
+      <c r="A33" s="242" t="n"/>
+      <c r="B33" s="266" t="n"/>
+      <c r="C33" s="267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="267" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="267" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="219" t="n"/>
+      <c r="H33" s="220" t="n"/>
+    </row>
+    <row r="34" ht="14.4" customHeight="1">
+      <c r="A34" s="268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2.2 ما هو حالة المطبخ 
+(الحد الأدنى من المساحة الكافية للمطبخ 9متر مكعب) </t>
+        </is>
+      </c>
+      <c r="B34" s="263" t="n"/>
+      <c r="C34" s="264" t="inlineStr">
+        <is>
+          <t>حالة جيد وقياس جيد
+(المساحة ≥ 9متر مكعب )</t>
+        </is>
+      </c>
+      <c r="D34" s="264" t="inlineStr">
+        <is>
+          <t>حالة جيد وقياس سيء
+(المساحة ˂ 9امتر مكعب)</t>
+        </is>
+      </c>
+      <c r="E34" s="264" t="inlineStr">
+        <is>
+          <t>حالة سيئة وقياس جيد
+(المساحة ≥9امتر مكعب)</t>
+        </is>
+      </c>
+      <c r="F34" s="264" t="inlineStr">
+        <is>
+          <t>حالة سيئة وقياس سيء
+(المساحة ˂ 9امتر مكعب)</t>
+        </is>
+      </c>
+      <c r="G34" s="214" t="n"/>
+      <c r="H34" s="215" t="n"/>
+    </row>
+    <row r="35" ht="15.6" customHeight="1">
+      <c r="A35" s="242" t="n"/>
+      <c r="B35" s="266" t="n"/>
+      <c r="C35" s="267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="267" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="267" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="267" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="219" t="n"/>
+      <c r="H35" s="220" t="n"/>
+    </row>
+    <row r="36" ht="14.4" customHeight="1">
+      <c r="A36" s="268" t="inlineStr">
+        <is>
+          <t>3.2.3 ما مدى جودة تهوية المأوى والاضاءة 
+(النسبة المئوية من الغرف التي لها نوافذ كافية وتوفر الضوء والتهوية مقابل إجمالي عدد الغرف)</t>
+        </is>
+      </c>
+      <c r="B36" s="263" t="n"/>
+      <c r="C36" s="265" t="inlineStr">
+        <is>
+          <t>˂  50%</t>
+        </is>
+      </c>
+      <c r="D36" s="265" t="inlineStr">
+        <is>
+          <t>50-75%</t>
+        </is>
+      </c>
+      <c r="E36" s="265" t="inlineStr">
+        <is>
+          <t>˃ 75%</t>
+        </is>
+      </c>
+      <c r="F36" s="269" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="214" t="n"/>
+      <c r="H36" s="215" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="242" t="n"/>
+      <c r="B37" s="266" t="n"/>
+      <c r="C37" s="267" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="156" t="inlineStr">
-        <is>
-          <t>2.2.2 عدد افراد الاسرة الذين ينامون بغرفة نوم واحدة</t>
-        </is>
-      </c>
-      <c r="G18" s="148" t="n"/>
-      <c r="H18" s="155" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="156" t="inlineStr">
-        <is>
-          <t>2.2.3 هل يوجد فصل بين الجنسين لعمر فوق 10 سنوات</t>
-        </is>
-      </c>
-      <c r="G19" s="148" t="n"/>
-      <c r="H19" s="155" t="n">
+      <c r="D37" s="267" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="156" t="inlineStr">
-        <is>
-          <t>2.2.4 هل للأسرة دخل منتظم؟</t>
-        </is>
-      </c>
-      <c r="G20" s="148" t="n"/>
-      <c r="H20" s="155" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="151" t="inlineStr">
-        <is>
-          <t>3. التقييم المادي</t>
-        </is>
-      </c>
-      <c r="B21" s="146" t="n"/>
-      <c r="C21" s="146" t="n"/>
-      <c r="D21" s="146" t="n"/>
-      <c r="E21" s="146" t="n"/>
-      <c r="F21" s="147" t="n"/>
-      <c r="G21" s="148" t="n"/>
-      <c r="H21" s="155" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="156" t="inlineStr">
-        <is>
-          <t>3.1 سلامة هيكل البيت (الانحراف / التكسير / التفلطح / الاستقرار)</t>
-        </is>
-      </c>
-      <c r="C22" s="157" t="n"/>
-      <c r="D22" s="157" t="n"/>
-      <c r="E22" s="157" t="n"/>
-      <c r="F22" s="157" t="n"/>
-      <c r="G22" s="148" t="n"/>
-      <c r="H22" s="155" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="151" t="inlineStr">
-        <is>
-          <t>3.2 الظروف الأخرى للبيت (بشكل جزئي)</t>
-        </is>
-      </c>
-      <c r="B23" s="146" t="n"/>
-      <c r="C23" s="146" t="n"/>
-      <c r="D23" s="146" t="n"/>
-      <c r="E23" s="146" t="n"/>
-      <c r="F23" s="147" t="n"/>
-      <c r="G23" s="148" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="156" t="inlineStr">
-        <is>
-          <t>3.2.1 حالة المرحاض (النظافة والمساحة)</t>
-        </is>
-      </c>
-      <c r="G24" s="148" t="n"/>
-      <c r="H24" s="155" t="n">
+      <c r="E37" s="267" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="219" t="n"/>
+      <c r="H37" s="220" t="n"/>
+    </row>
+    <row r="38" ht="15.6" customHeight="1">
+      <c r="A38" s="268" t="inlineStr">
+        <is>
+          <t>3.2.4 ما هي مؤشرات الرطوبة في البيت?
+(النسبة المئوية من الغرف التي بها رطوبة مقابل إجمالي عدد الغرف)</t>
+        </is>
+      </c>
+      <c r="B38" s="263" t="n"/>
+      <c r="C38" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (No dampness = 0)</t>
+        </is>
+      </c>
+      <c r="D38" s="265" t="inlineStr">
+        <is>
+          <t>(25% = 3)</t>
+        </is>
+      </c>
+      <c r="E38" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (50-75% = 5)</t>
+        </is>
+      </c>
+      <c r="F38" s="269" t="inlineStr">
+        <is>
+          <t>(100% = 8)</t>
+        </is>
+      </c>
+      <c r="G38" s="214" t="n"/>
+      <c r="H38" s="215" t="n"/>
+    </row>
+    <row r="39" ht="15.6" customHeight="1">
+      <c r="A39" s="242" t="n"/>
+      <c r="B39" s="266" t="n"/>
+      <c r="C39" s="267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="267" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="156" t="inlineStr">
-        <is>
-          <t>3.2.2 حالة المطبخ (النظافة والمساحة)</t>
-        </is>
-      </c>
-      <c r="G25" s="148" t="n"/>
-      <c r="H25" s="155" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="156" t="inlineStr">
-        <is>
-          <t>3.2.3 جودة تهوية المأوى والإضاءة</t>
-        </is>
-      </c>
-      <c r="G26" s="148" t="n"/>
-      <c r="H26" s="155" t="n">
+      <c r="F39" s="267" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="156" t="inlineStr">
-        <is>
-          <t>3.2.4 مؤشرات الرطوبة في البيت</t>
-        </is>
-      </c>
-      <c r="G27" s="148" t="n"/>
-      <c r="H27" s="155" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="156" t="inlineStr">
-        <is>
-          <t>3.2.5 طريقة وصل البيت بشبكة الصرف الصحي</t>
-        </is>
-      </c>
-      <c r="G28" s="148" t="n"/>
-      <c r="H28" s="155" t="n">
+      <c r="G39" s="219" t="n"/>
+      <c r="H39" s="220" t="n"/>
+    </row>
+    <row r="40" ht="31.2" customHeight="1">
+      <c r="A40" s="270" t="inlineStr">
+        <is>
+          <t>3.2.5 ما هي طريقة وصل البيت بشبكة الصرف الصحي</t>
+        </is>
+      </c>
+      <c r="B40" s="271" t="n"/>
+      <c r="C40" s="265" t="inlineStr">
+        <is>
+          <t>لا يوجد اتصال</t>
+        </is>
+      </c>
+      <c r="D40" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اتصال بحفرة التخلص من الصرف الصحي </t>
+        </is>
+      </c>
+      <c r="E40" s="272" t="inlineStr">
+        <is>
+          <t>يوجد اتصال بشبكة الصرف الصحي بشكل غير ملائم</t>
+        </is>
+      </c>
+      <c r="F40" s="265" t="inlineStr">
+        <is>
+          <t>اتصال ملائم بشبكة الصرف الصحي</t>
+        </is>
+      </c>
+      <c r="G40" s="225" t="n"/>
+      <c r="H40" s="215" t="n"/>
+    </row>
+    <row r="41" ht="16.2" customHeight="1">
+      <c r="A41" s="238" t="n"/>
+      <c r="B41" s="239" t="n"/>
+      <c r="C41" s="273" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="158" t="inlineStr">
-        <is>
-          <t>النتيجة الاجمالية النهائية (من 100)</t>
-        </is>
-      </c>
-      <c r="B29" s="146" t="n"/>
-      <c r="C29" s="146" t="n"/>
-      <c r="D29" s="146" t="n"/>
-      <c r="E29" s="146" t="n"/>
-      <c r="F29" s="147" t="n"/>
-      <c r="G29" s="159" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="160" t="inlineStr">
-        <is>
-          <t>مصدر البيانات: استمارة تقييم كوبو 2026 — قيم منسوخة تلقائيًا من نسخة مستوردة على هذا الجهاز، بدون أي ربط حي.</t>
-        </is>
-      </c>
+      <c r="D41" s="273" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="228" t="n"/>
+      <c r="H41" s="229" t="n"/>
+    </row>
+    <row r="42" ht="25.95" customHeight="1">
+      <c r="A42" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النتيجة الاجمالية النهائية </t>
+        </is>
+      </c>
+      <c r="B42" s="147" t="n"/>
+      <c r="C42" s="147" t="n"/>
+      <c r="D42" s="147" t="n"/>
+      <c r="E42" s="147" t="n"/>
+      <c r="F42" s="155" t="n"/>
+      <c r="G42" s="204" t="n"/>
+      <c r="H42" s="155" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="n"/>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="n"/>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="23" t="n"/>
+      <c r="F44" s="23" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="G47" s="275" t="n"/>
+      <c r="H47" s="276" t="n"/>
+    </row>
+    <row r="48">
+      <c r="G48" s="275" t="n"/>
+      <c r="H48" s="276" t="n"/>
+    </row>
+    <row r="49">
+      <c r="G49" s="275" t="n"/>
+      <c r="H49" s="276" t="n"/>
+    </row>
+    <row r="50" ht="15.6" customHeight="1">
+      <c r="A50" s="277" t="n"/>
+      <c r="B50" s="276" t="n"/>
+      <c r="C50" s="278" t="n"/>
+      <c r="D50" s="279" t="n"/>
+      <c r="E50" s="279" t="n"/>
+      <c r="F50" s="278" t="n"/>
+      <c r="G50" s="275" t="n"/>
+      <c r="H50" s="276" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="276" t="n"/>
+      <c r="B51" s="276" t="n"/>
+      <c r="C51" s="280" t="n"/>
+      <c r="D51" s="280" t="n"/>
+      <c r="E51" s="281" t="n"/>
+      <c r="F51" s="281" t="n"/>
+      <c r="G51" s="276" t="n"/>
+      <c r="H51" s="276" t="n"/>
+    </row>
+    <row r="52" ht="15.6" customHeight="1">
+      <c r="A52" s="277" t="n"/>
+      <c r="B52" s="276" t="n"/>
+      <c r="C52" s="278" t="n"/>
+      <c r="D52" s="279" t="n"/>
+      <c r="E52" s="279" t="n"/>
+      <c r="F52" s="278" t="n"/>
+      <c r="G52" s="275" t="n"/>
+      <c r="H52" s="276" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="276" t="n"/>
+      <c r="B53" s="276" t="n"/>
+      <c r="C53" s="280" t="n"/>
+      <c r="D53" s="280" t="n"/>
+      <c r="E53" s="281" t="n"/>
+      <c r="F53" s="281" t="n"/>
+      <c r="G53" s="276" t="n"/>
+      <c r="H53" s="276" t="n"/>
+    </row>
+    <row r="54" ht="15.6" customHeight="1">
+      <c r="A54" s="277" t="n"/>
+      <c r="B54" s="276" t="n"/>
+      <c r="C54" s="278" t="n"/>
+      <c r="D54" s="279" t="n"/>
+      <c r="E54" s="279" t="n"/>
+      <c r="F54" s="278" t="n"/>
+      <c r="G54" s="275" t="n"/>
+      <c r="H54" s="276" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="276" t="n"/>
+      <c r="B55" s="276" t="n"/>
+      <c r="C55" s="280" t="n"/>
+      <c r="D55" s="280" t="n"/>
+      <c r="E55" s="281" t="n"/>
+      <c r="F55" s="281" t="n"/>
+      <c r="G55" s="276" t="n"/>
+      <c r="H55" s="276" t="n"/>
+    </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="277" t="n"/>
+      <c r="B58" s="276" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="276" t="n"/>
+      <c r="B59" s="276" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="51">
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A28:B30"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="G54:H55"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="G50:H51"/>
+    <mergeCell ref="G32:H33"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="A38:B39"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A52:B53"/>
+    <mergeCell ref="A34:B35"/>
+    <mergeCell ref="G21:H22"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A40:B41"/>
+    <mergeCell ref="G40:H41"/>
+    <mergeCell ref="G28:H30"/>
+    <mergeCell ref="A58:B59"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="G36:H37"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="G52:H53"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="A54:B55"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="G34:H35"/>
+    <mergeCell ref="A50:B51"/>
+    <mergeCell ref="G19:H20"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="A25:B26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2964,53 +4868,53 @@
   <sheetData>
     <row r="1" ht="9" customHeight="1" thickBot="1"/>
     <row r="2" ht="29.25" customHeight="1" thickBot="1" thickTop="1">
-      <c r="B2" s="161" t="inlineStr">
+      <c r="B2" s="282" t="inlineStr">
         <is>
           <t>ملحق رقم  "1 "</t>
         </is>
       </c>
-      <c r="C2" s="162" t="n"/>
-      <c r="D2" s="162" t="n"/>
-      <c r="E2" s="162" t="n"/>
-      <c r="F2" s="162" t="n"/>
-      <c r="G2" s="162" t="n"/>
-      <c r="H2" s="162" t="n"/>
-      <c r="I2" s="162" t="n"/>
-      <c r="J2" s="163" t="n"/>
+      <c r="C2" s="283" t="n"/>
+      <c r="D2" s="283" t="n"/>
+      <c r="E2" s="283" t="n"/>
+      <c r="F2" s="283" t="n"/>
+      <c r="G2" s="283" t="n"/>
+      <c r="H2" s="283" t="n"/>
+      <c r="I2" s="283" t="n"/>
+      <c r="J2" s="284" t="n"/>
     </row>
     <row r="3" ht="33" customHeight="1" thickBot="1" thickTop="1">
-      <c r="B3" s="164" t="inlineStr">
+      <c r="B3" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve">        Bill of Quantités  فاتورة الكميات</t>
         </is>
       </c>
-      <c r="C3" s="162" t="n"/>
-      <c r="D3" s="162" t="n"/>
-      <c r="E3" s="162" t="n"/>
-      <c r="F3" s="163" t="n"/>
+      <c r="C3" s="283" t="n"/>
+      <c r="D3" s="283" t="n"/>
+      <c r="E3" s="283" t="n"/>
+      <c r="F3" s="284" t="n"/>
       <c r="G3" s="134" t="inlineStr">
         <is>
           <t>اسم المستفيد</t>
         </is>
       </c>
-      <c r="H3" s="162" t="n"/>
-      <c r="I3" s="165" t="n"/>
-      <c r="J3" s="163" t="n"/>
+      <c r="H3" s="283" t="n"/>
+      <c r="I3" s="286" t="n"/>
+      <c r="J3" s="284" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1" thickBot="1" thickTop="1">
-      <c r="B4" s="166" t="inlineStr">
+      <c r="B4" s="287" t="inlineStr">
         <is>
           <t xml:space="preserve">The below table must be filled by a qualified engineer </t>
         </is>
       </c>
-      <c r="C4" s="167" t="n"/>
-      <c r="D4" s="167" t="n"/>
-      <c r="E4" s="167" t="n"/>
-      <c r="F4" s="167" t="n"/>
-      <c r="G4" s="167" t="n"/>
-      <c r="H4" s="167" t="n"/>
-      <c r="I4" s="167" t="n"/>
-      <c r="J4" s="168" t="n"/>
+      <c r="C4" s="288" t="n"/>
+      <c r="D4" s="288" t="n"/>
+      <c r="E4" s="288" t="n"/>
+      <c r="F4" s="288" t="n"/>
+      <c r="G4" s="288" t="n"/>
+      <c r="H4" s="288" t="n"/>
+      <c r="I4" s="288" t="n"/>
+      <c r="J4" s="289" t="n"/>
     </row>
     <row r="5" ht="35.1" customHeight="1" thickBot="1" thickTop="1">
       <c r="B5" s="107" t="inlineStr">
@@ -3023,7 +4927,7 @@
           <t xml:space="preserve">Type of damage  </t>
         </is>
       </c>
-      <c r="D5" s="169" t="n"/>
+      <c r="D5" s="290" t="n"/>
       <c r="E5" s="94" t="inlineStr">
         <is>
           <t xml:space="preserve">Unit  </t>
@@ -3056,13 +4960,13 @@
       </c>
     </row>
     <row r="6" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B6" s="170" t="n"/>
+      <c r="B6" s="291" t="n"/>
       <c r="C6" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve"> نوع الضرر</t>
         </is>
       </c>
-      <c r="D6" s="171" t="n"/>
+      <c r="D6" s="292" t="n"/>
       <c r="E6" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve"> واحدة </t>
@@ -3140,7 +5044,7 @@
       <c r="B8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="172" t="n"/>
+      <c r="C8" s="293" t="n"/>
       <c r="D8" s="61" t="inlineStr">
         <is>
           <t>تدعيم معدني</t>
@@ -3175,7 +5079,7 @@
       <c r="B9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="172" t="n"/>
+      <c r="C9" s="293" t="n"/>
       <c r="D9" s="59" t="inlineStr">
         <is>
           <t>بلوك</t>
@@ -3211,7 +5115,7 @@
       <c r="B10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="172" t="n"/>
+      <c r="C10" s="293" t="n"/>
       <c r="D10" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  طينة اسمنتية  </t>
@@ -3250,7 +5154,7 @@
       <c r="B11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="172" t="n"/>
+      <c r="C11" s="293" t="n"/>
       <c r="D11" s="59" t="inlineStr">
         <is>
           <t>طينة غراوت</t>
@@ -3285,7 +5189,7 @@
       <c r="B12" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="173" t="n"/>
+      <c r="C12" s="294" t="n"/>
       <c r="D12" s="63" t="inlineStr">
         <is>
           <t>مداخن</t>
@@ -3320,7 +5224,7 @@
       <c r="B13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="174" t="inlineStr">
+      <c r="C13" s="295" t="inlineStr">
         <is>
           <t xml:space="preserve"> الأرضية والجدران</t>
         </is>
@@ -3363,7 +5267,7 @@
       <c r="B14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="172" t="n"/>
+      <c r="C14" s="293" t="n"/>
       <c r="D14" s="61" t="inlineStr">
         <is>
           <t>نعلة بلاط</t>
@@ -3398,7 +5302,7 @@
       <c r="B15" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="172" t="n"/>
+      <c r="C15" s="293" t="n"/>
       <c r="D15" s="59" t="inlineStr">
         <is>
           <t>جلي بلاط</t>
@@ -3433,7 +5337,7 @@
       <c r="B16" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="173" t="n"/>
+      <c r="C16" s="294" t="n"/>
       <c r="D16" s="63" t="inlineStr">
         <is>
           <t>سيراميك</t>
@@ -3510,7 +5414,7 @@
       <c r="B18" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="174" t="inlineStr">
+      <c r="C18" s="295" t="inlineStr">
         <is>
           <t>أعمال النجارة</t>
         </is>
@@ -3552,7 +5456,7 @@
       <c r="B19" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="172" t="n"/>
+      <c r="C19" s="293" t="n"/>
       <c r="D19" s="59" t="inlineStr">
         <is>
           <t>ملابن</t>
@@ -3587,7 +5491,7 @@
       <c r="B20" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="172" t="n"/>
+      <c r="C20" s="293" t="n"/>
       <c r="D20" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve"> صيانة أبواب </t>
@@ -3622,7 +5526,7 @@
       <c r="B21" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="173" t="n"/>
+      <c r="C21" s="294" t="n"/>
       <c r="D21" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve"> صيانة نوافذ </t>
@@ -3657,7 +5561,7 @@
       <c r="B22" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="175" t="inlineStr">
+      <c r="C22" s="296" t="inlineStr">
         <is>
           <t>أعمال الألمنيوم</t>
         </is>
@@ -3698,7 +5602,7 @@
       <c r="B23" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="172" t="n"/>
+      <c r="C23" s="293" t="n"/>
       <c r="D23" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve"> نوافذ ألمنيوم</t>
@@ -3739,7 +5643,7 @@
       <c r="B24" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="C24" s="173" t="n"/>
+      <c r="C24" s="294" t="n"/>
       <c r="D24" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve"> صيانة </t>
@@ -3777,7 +5681,7 @@
       <c r="B25" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="176" t="inlineStr">
+      <c r="C25" s="297" t="inlineStr">
         <is>
           <t>أعمال الحديد</t>
         </is>
@@ -3817,7 +5721,7 @@
       <c r="B26" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="173" t="n"/>
+      <c r="C26" s="294" t="n"/>
       <c r="D26" s="76" t="inlineStr">
         <is>
           <t>صيانة حديد</t>
@@ -3896,7 +5800,7 @@
       <c r="B28" s="38" t="n">
         <v>22</v>
       </c>
-      <c r="C28" s="174" t="inlineStr">
+      <c r="C28" s="295" t="inlineStr">
         <is>
           <t xml:space="preserve">أعمال الصحية  </t>
         </is>
@@ -3936,7 +5840,7 @@
       <c r="B29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="C29" s="172" t="n"/>
+      <c r="C29" s="293" t="n"/>
       <c r="D29" s="59" t="inlineStr">
         <is>
           <t>مغسلة</t>
@@ -3971,7 +5875,7 @@
       <c r="B30" s="40" t="n">
         <v>24</v>
       </c>
-      <c r="C30" s="172" t="n"/>
+      <c r="C30" s="293" t="n"/>
       <c r="D30" s="81" t="inlineStr">
         <is>
           <t>مرحاض عربي</t>
@@ -4007,7 +5911,7 @@
       <c r="B31" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="C31" s="172" t="n"/>
+      <c r="C31" s="293" t="n"/>
       <c r="D31" s="59" t="inlineStr">
         <is>
           <t>مرحاض فرنجي</t>
@@ -4043,7 +5947,7 @@
       <c r="B32" s="40" t="n">
         <v>26</v>
       </c>
-      <c r="C32" s="172" t="n"/>
+      <c r="C32" s="293" t="n"/>
       <c r="D32" s="81" t="inlineStr">
         <is>
           <t>سواد مالحة</t>
@@ -4081,7 +5985,7 @@
       <c r="B33" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="C33" s="172" t="n"/>
+      <c r="C33" s="293" t="n"/>
       <c r="D33" s="59" t="inlineStr">
         <is>
           <t>سواد حلوة</t>
@@ -4118,7 +6022,7 @@
       <c r="B34" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="C34" s="172" t="n"/>
+      <c r="C34" s="293" t="n"/>
       <c r="D34" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">بياض صحية </t>
@@ -4153,7 +6057,7 @@
       <c r="B35" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="C35" s="172" t="n"/>
+      <c r="C35" s="293" t="n"/>
       <c r="D35" s="59" t="inlineStr">
         <is>
           <t>مضخة مياه</t>
@@ -4188,7 +6092,7 @@
       <c r="B36" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="C36" s="173" t="n"/>
+      <c r="C36" s="294" t="n"/>
       <c r="D36" s="85" t="inlineStr">
         <is>
           <t>خزان ماء</t>
@@ -4225,7 +6129,7 @@
       <c r="B37" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="C37" s="175" t="inlineStr">
+      <c r="C37" s="296" t="inlineStr">
         <is>
           <t>أعمال الكهرباء</t>
         </is>
@@ -4265,7 +6169,7 @@
       <c r="B38" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="C38" s="172" t="n"/>
+      <c r="C38" s="293" t="n"/>
       <c r="D38" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">كبل تغذيةكهربائي </t>
@@ -4302,7 +6206,7 @@
       <c r="B39" s="34" t="n">
         <v>33</v>
       </c>
-      <c r="C39" s="172" t="n"/>
+      <c r="C39" s="293" t="n"/>
       <c r="D39" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">لوحة قواطع </t>
@@ -4337,7 +6241,7 @@
       <c r="B40" s="43" t="n">
         <v>34</v>
       </c>
-      <c r="C40" s="172" t="n"/>
+      <c r="C40" s="293" t="n"/>
       <c r="D40" s="81" t="inlineStr">
         <is>
           <t>بياض كهرباء</t>
@@ -4376,7 +6280,7 @@
       <c r="B41" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="C41" s="172" t="n"/>
+      <c r="C41" s="293" t="n"/>
       <c r="D41" s="59" t="inlineStr">
         <is>
           <t>سخان كهربائي</t>
@@ -4412,7 +6316,7 @@
       <c r="B42" s="44" t="n">
         <v>36</v>
       </c>
-      <c r="C42" s="173" t="n"/>
+      <c r="C42" s="294" t="n"/>
       <c r="D42" s="85" t="inlineStr">
         <is>
           <t>شفاط كهربائي</t>
@@ -4486,21 +6390,21 @@
           <t>المجموع النهائي</t>
         </is>
       </c>
-      <c r="C44" s="162" t="n"/>
-      <c r="D44" s="177" t="n"/>
-      <c r="E44" s="178">
+      <c r="C44" s="283" t="n"/>
+      <c r="D44" s="298" t="n"/>
+      <c r="E44" s="299">
         <f>SUM(H7:H43)</f>
         <v/>
       </c>
-      <c r="F44" s="162" t="n"/>
-      <c r="G44" s="162" t="n"/>
-      <c r="H44" s="163" t="n"/>
-      <c r="I44" s="179" t="inlineStr">
+      <c r="F44" s="283" t="n"/>
+      <c r="G44" s="283" t="n"/>
+      <c r="H44" s="284" t="n"/>
+      <c r="I44" s="300" t="inlineStr">
         <is>
           <t xml:space="preserve">ملاحظة :بالنسبة لجميع المواد يتم استخدام المواد الأساسية ذات الجودة القياسية المتاحة في السوق المحلية </t>
         </is>
       </c>
-      <c r="J44" s="163" t="n"/>
+      <c r="J44" s="284" t="n"/>
     </row>
     <row r="45" ht="45" customHeight="1" thickBot="1" thickTop="1">
       <c r="B45" s="113" t="inlineStr">
@@ -4508,24 +6412,24 @@
           <t>الدفعة الأولى</t>
         </is>
       </c>
-      <c r="C45" s="162" t="n"/>
-      <c r="D45" s="177" t="n"/>
-      <c r="E45" s="180">
+      <c r="C45" s="283" t="n"/>
+      <c r="D45" s="298" t="n"/>
+      <c r="E45" s="301">
         <f>E44*0.6</f>
         <v/>
       </c>
-      <c r="F45" s="162" t="n"/>
-      <c r="G45" s="163" t="n"/>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="284" t="n"/>
       <c r="H45" s="58" t="inlineStr">
         <is>
           <t>الدفعة الثانية</t>
         </is>
       </c>
-      <c r="I45" s="181">
+      <c r="I45" s="302">
         <f>E44*0.4</f>
         <v/>
       </c>
-      <c r="J45" s="163" t="n"/>
+      <c r="J45" s="284" t="n"/>
     </row>
     <row r="46" ht="16.2" customHeight="1" thickTop="1"/>
   </sheetData>
@@ -4642,7 +6546,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" thickTop="1">
       <c r="A3" s="32" t="n"/>
-      <c r="B3" s="182" t="inlineStr">
+      <c r="B3" s="303" t="inlineStr">
         <is>
           <t>الإسم</t>
         </is>
@@ -4653,7 +6557,7 @@
         </is>
       </c>
       <c r="D3" s="30" t="n"/>
-      <c r="E3" s="183" t="inlineStr">
+      <c r="E3" s="304" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
@@ -4661,7 +6565,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="32" t="n"/>
-      <c r="B4" s="184" t="n"/>
+      <c r="B4" s="305" t="n"/>
       <c r="C4" s="31" t="inlineStr">
         <is>
           <t>النسبة %</t>
@@ -4672,7 +6576,7 @@
           <t>التقرير</t>
         </is>
       </c>
-      <c r="E4" s="185" t="n"/>
+      <c r="E4" s="306" t="n"/>
     </row>
     <row r="5" ht="45.75" customHeight="1" thickBot="1" thickTop="1">
       <c r="B5" s="27">

--- a/app/src/main/assets/quantities_template.xlsx
+++ b/app/src/main/assets/quantities_template.xlsx
@@ -3371,19 +3371,9 @@
       </c>
       <c r="B1" s="146" t="n"/>
       <c r="C1" s="147" t="n"/>
-      <c r="D1" s="148" t="inlineStr">
-        <is>
-          <t>بشار العطية</t>
-        </is>
-      </c>
-      <c r="E1" s="149" t="inlineStr">
-        <is>
-          <t>مريم ابو عطوان</t>
-        </is>
-      </c>
-      <c r="F1" s="149" t="n">
-        <v>46047.55154947917</v>
-      </c>
+      <c r="D1" s="148" t="n"/>
+      <c r="E1" s="149" t="n"/>
+      <c r="F1" s="149" t="n"/>
       <c r="G1" s="150" t="inlineStr">
         <is>
           <t>زيارة الترميم</t>
@@ -3464,9 +3454,7 @@
           <t>عدد الاسر في المنزل</t>
         </is>
       </c>
-      <c r="H4" s="170" t="n">
-        <v>1</v>
-      </c>
+      <c r="H4" s="170" t="n"/>
     </row>
     <row r="5" ht="17.4" customHeight="1">
       <c r="A5" s="163" t="inlineStr">
@@ -3511,9 +3499,7 @@
         </is>
       </c>
       <c r="D6" s="164" t="n"/>
-      <c r="E6" s="174" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" s="174" t="n"/>
       <c r="F6" s="175" t="inlineStr">
         <is>
           <t>ملكية البيت مشتركة/ خاصة</t>
@@ -3605,11 +3591,7 @@
           <t>الطابق</t>
         </is>
       </c>
-      <c r="F10" s="196" t="inlineStr">
-        <is>
-          <t>بناء طابقي ( شقة سكنية)</t>
-        </is>
-      </c>
+      <c r="F10" s="196" t="n"/>
       <c r="G10" s="197" t="n"/>
       <c r="H10" s="198" t="n"/>
     </row>
